--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N37_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N37_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>48.19617199514525</v>
+        <v>7.831877949211103</v>
       </c>
       <c r="D2" t="n">
-        <v>47.97374810344047</v>
+        <v>7.795734066809077</v>
       </c>
       <c r="E2" t="n">
-        <v>12.98100655021454</v>
+        <v>2.109413564409863</v>
       </c>
       <c r="F2" t="n">
-        <v>17.04226752734914</v>
+        <v>2.769368473194235</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>52.85444035388114</v>
+        <v>8.588846557505684</v>
       </c>
       <c r="D3" t="n">
-        <v>38.8433890691569</v>
+        <v>6.312050723737996</v>
       </c>
       <c r="E3" t="n">
-        <v>12.98100655021454</v>
+        <v>2.109413564409863</v>
       </c>
       <c r="F3" t="n">
-        <v>17.04226752734914</v>
+        <v>2.769368473194235</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>37.16398913389345</v>
+        <v>6.039148234257686</v>
       </c>
       <c r="D4" t="n">
-        <v>26.61094966726382</v>
+        <v>4.32427932093037</v>
       </c>
       <c r="E4" t="n">
-        <v>12.98100655021454</v>
+        <v>2.109413564409863</v>
       </c>
       <c r="F4" t="n">
-        <v>17.04226752734914</v>
+        <v>2.769368473194235</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.22260152551615</v>
+        <v>3.448672747896374</v>
       </c>
       <c r="D5" t="n">
-        <v>15.15506776532304</v>
+        <v>2.462698511864995</v>
       </c>
       <c r="E5" t="n">
-        <v>12.98100655021454</v>
+        <v>2.109413564409863</v>
       </c>
       <c r="F5" t="n">
-        <v>17.04226752734914</v>
+        <v>2.769368473194235</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>16.96026690113571</v>
+        <v>2.756043371434553</v>
       </c>
       <c r="D6" t="n">
-        <v>6.358417215708172</v>
+        <v>1.033242797552578</v>
       </c>
       <c r="E6" t="n">
-        <v>12.98100655021454</v>
+        <v>2.109413564409863</v>
       </c>
       <c r="F6" t="n">
-        <v>17.04226752734914</v>
+        <v>2.769368473194235</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>28.00227760415942</v>
+        <v>4.550370110675906</v>
       </c>
       <c r="D7" t="n">
-        <v>58.33395513245929</v>
+        <v>9.479267709024636</v>
       </c>
       <c r="E7" t="n">
-        <v>12.98100655021454</v>
+        <v>2.109413564409863</v>
       </c>
       <c r="F7" t="n">
-        <v>17.04226752734914</v>
+        <v>2.769368473194235</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>42.32411065074614</v>
+        <v>6.877667980746248</v>
       </c>
       <c r="D8" t="n">
-        <v>52.47069334570129</v>
+        <v>8.526487668676459</v>
       </c>
       <c r="E8" t="n">
-        <v>12.98100655021454</v>
+        <v>2.109413564409863</v>
       </c>
       <c r="F8" t="n">
-        <v>17.04226752734914</v>
+        <v>2.769368473194235</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>18.9274932307477</v>
+        <v>3.075717649996502</v>
       </c>
       <c r="D9" t="n">
-        <v>37.78230868608058</v>
+        <v>6.139625161488095</v>
       </c>
       <c r="E9" t="n">
-        <v>12.98100655021454</v>
+        <v>2.109413564409863</v>
       </c>
       <c r="F9" t="n">
-        <v>17.04226752734914</v>
+        <v>2.769368473194235</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
